--- a/studies/solaire-afrique/etude_solaire_afrique.xlsx
+++ b/studies/solaire-afrique/etude_solaire_afrique.xlsx
@@ -15,8 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volet_C" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modele_LCOE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verif_proposition" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reperes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthese" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modele_LCOE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modele_B_captif" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modele_C_minireseau" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verif_proposition" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,9 +29,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -83,20 +88,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -523,36 +531,64 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5. PV+stockage et solaire thermodynamique (CSP) sont analysés à part.</t>
+          <t>5. Les trois volets sont comparés séparément : Synthese calcule chaque statistique dans un seul</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6. Le LCOE est toujours calculé (Modele_LCOE), jamais saisi comme donnée observée.</t>
+          <t xml:space="preserve">   volet, et les repères agrégés (Reperes) portent leur volet. Dans le volet A, PV+stockage et</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   solaire thermodynamique (CSP) sont analysés à part du PV seul.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>État actuel : 4 projets partiellement renseignés (Zambie, Sénégal) ; les autres lignes sont des</t>
+          <t>6. Modèles : Modele_LCOE (volet A), Modele_B_captif (solaire contre diesel),</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>candidats issus de la proposition, marqués « à vérifier », sans chiffres.</t>
+          <t xml:space="preserve">   Modele_C_minireseau (coût complet du service et subvention).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
+        <is>
+          <t>7. Le LCOE est toujours calculé, jamais saisi comme donnée observée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>État actuel : volet A, 4 projets partiellement renseignés (Zambie, Sénégal) et 4 candidats « à vérifier »</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sans chiffres ; volet B, 2 projets miniers (Mali, Mauritanie) ; volet C, 1 mini-réseau (RDC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Les cibles de 100 / 75 / 125 projets sont des objectifs de collecte, pas des projets identifiés.</t>
         </is>
@@ -564,6 +600,2834 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Synthèse par volet : chaque statistique est calculée à l'intérieur d'un seul volet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Les moyennes ne portent que sur les projets « en service » renseignés. Avec si peu de projets, elles ne sont pas représentatives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>volet</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>indicateur</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>en service</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>en construction</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>attribué</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>annoncé</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>abandonné</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>nombre de projets</t>
+        </is>
+      </c>
+      <c r="C5">
+        <f>COUNTIF(Volet_A!F:F,"en service")</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>COUNTIF(Volet_A!F:F,"en construction")</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>COUNTIF(Volet_A!F:F,"attribué")</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>COUNTIF(Volet_A!F:F,"annoncé")</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>COUNTIF(Volet_A!F:F,"à vérifier")</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>COUNTIF(Volet_A!F:F,"abandonné")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>nombre de projets</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>COUNTIF(Volet_B!F:F,"en service")</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>COUNTIF(Volet_B!F:F,"en construction")</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>COUNTIF(Volet_B!F:F,"attribué")</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>COUNTIF(Volet_B!F:F,"annoncé")</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>COUNTIF(Volet_B!F:F,"à vérifier")</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>COUNTIF(Volet_B!F:F,"abandonné")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nombre de projets</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>COUNTIF(Volet_C!F:F,"en service")</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>COUNTIF(Volet_C!F:F,"en construction")</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>COUNTIF(Volet_C!F:F,"attribué")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>COUNTIF(Volet_C!F:F,"annoncé")</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>COUNTIF(Volet_C!F:F,"à vérifier")</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>COUNTIF(Volet_C!F:F,"abandonné")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>volet</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>indicateur (projets en service)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>moyenne</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>capex_usd_kwac</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>COUNTIFS(Volet_A!F2:F2000,"en service",Volet_A!Q2:Q2000,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>IFERROR(AVERAGEIFS(Volet_A!Q2:Q2000,Volet_A!F2:F2000,"en service"),"")</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>IF(C10=0,"",MINIFS(Volet_A!Q2:Q2000,Volet_A!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>IF(C10=0,"",MAXIFS(Volet_A!Q2:Q2000,Volet_A!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lcoe_usd_mwh</t>
+        </is>
+      </c>
+      <c r="C11">
+        <f>COUNTIFS(Volet_A!F2:F2000,"en service",Volet_A!AE2:AE2000,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>IFERROR(AVERAGEIFS(Volet_A!AE2:AE2000,Volet_A!F2:F2000,"en service"),"")</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>IF(C11=0,"",MINIFS(Volet_A!AE2:AE2000,Volet_A!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>IF(C11=0,"",MAXIFS(Volet_A!AE2:AE2000,Volet_A!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>facteur_charge_ac</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>COUNTIFS(Volet_A!F2:F2000,"en service",Volet_A!S2:S2000,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>IFERROR(AVERAGEIFS(Volet_A!S2:S2000,Volet_A!F2:F2000,"en service"),"")</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>IF(C12=0,"",MINIFS(Volet_A!S2:S2000,Volet_A!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>IF(C12=0,"",MAXIFS(Volet_A!S2:S2000,Volet_A!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>capex_usd_kwp</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>COUNTIFS(Volet_B!F2:F2000,"en service",Volet_B!P2:P2000,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>IFERROR(AVERAGEIFS(Volet_B!P2:P2000,Volet_B!F2:F2000,"en service"),"")</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>IF(C13=0,"",MINIFS(Volet_B!P2:P2000,Volet_B!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>IF(C13=0,"",MAXIFS(Volet_B!P2:P2000,Volet_B!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>cout_diesel_evite_usd_mwh</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>COUNTIFS(Volet_B!F2:F2000,"en service",Volet_B!AK2:AK2000,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>IFERROR(AVERAGEIFS(Volet_B!AK2:AK2000,Volet_B!F2:F2000,"en service"),"")</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>IF(C14=0,"",MINIFS(Volet_B!AK2:AK2000,Volet_B!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>IF(C14=0,"",MAXIFS(Volet_B!AK2:AK2000,Volet_B!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>tri_projet</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>COUNTIFS(Volet_B!F2:F2000,"en service",Volet_B!AM2:AM2000,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>IFERROR(AVERAGEIFS(Volet_B!AM2:AM2000,Volet_B!F2:F2000,"en service"),"")</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>IF(C15=0,"",MINIFS(Volet_B!AM2:AM2000,Volet_B!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>IF(C15=0,"",MAXIFS(Volet_B!AM2:AM2000,Volet_B!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>capex_usd_kwp</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>COUNTIFS(Volet_C!F2:F2000,"en service",Volet_C!P2:P2000,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>IFERROR(AVERAGEIFS(Volet_C!P2:P2000,Volet_C!F2:F2000,"en service"),"")</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>IF(C16=0,"",MINIFS(Volet_C!P2:P2000,Volet_C!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>IF(C16=0,"",MAXIFS(Volet_C!P2:P2000,Volet_C!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>tarif_client</t>
+        </is>
+      </c>
+      <c r="C17">
+        <f>COUNTIFS(Volet_C!F2:F2000,"en service",Volet_C!AL2:AL2000,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>IFERROR(AVERAGEIFS(Volet_C!AL2:AL2000,Volet_C!F2:F2000,"en service"),"")</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>IF(C17=0,"",MINIFS(Volet_C!AL2:AL2000,Volet_C!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>IF(C17=0,"",MAXIFS(Volet_C!AL2:AL2000,Volet_C!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>subvention_usd</t>
+        </is>
+      </c>
+      <c r="C18">
+        <f>COUNTIFS(Volet_C!F2:F2000,"en service",Volet_C!AM2:AM2000,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>IFERROR(AVERAGEIFS(Volet_C!AM2:AM2000,Volet_C!F2:F2000,"en service"),"")</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>IF(C18=0,"",MINIFS(Volet_C!AM2:AM2000,Volet_C!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>IF(C18=0,"",MAXIFS(Volet_C!AM2:AM2000,Volet_C!F2:F2000,"en service"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Modèle LCOE — cellules jaunes modifiables. Investissement en année 0, flux en années 1..n.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Puissance</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MWp</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>année</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>OPEX (USD)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>production (MWh)</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>facteur d'actualisation</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Sensibilité au WACC (sans dégradation ni indexation : (CAPEX x CRF + OPEX) / E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAPEX spécifique</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>USD/kWp</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <f>IF(E4&lt;=$B$9,$B$20*(1+$B$7)^(E4-1),0)</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>IF(E4&lt;=$B$9,$B$19*(1-$B$8)^(E4-1),0)</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>1/(1+$B$17)^E4</f>
+        <v/>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>LCOE (USD/MWh)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>écart vs 4 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Production spécifique année 1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>kWh/kWp/an</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <f>IF(E5&lt;=$B$9,$B$20*(1+$B$7)^(E5-1),0)</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>IF(E5&lt;=$B$9,$B$19*(1-$B$8)^(E5-1),0)</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>1/(1+$B$17)^E5</f>
+        <v/>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K5" s="8">
+        <f>($B$18*J5*(1+J5)^$B$9/((1+J5)^$B$9-1)+$B$20)/$B$19</f>
+        <v/>
+      </c>
+      <c r="L5" s="9">
+        <f>K5/$K$5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OPEX année 1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>USD/kWp/an</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <f>IF(E6&lt;=$B$9,$B$20*(1+$B$7)^(E6-1),0)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>IF(E6&lt;=$B$9,$B$19*(1-$B$8)^(E6-1),0)</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>1/(1+$B$17)^E6</f>
+        <v/>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K6" s="8">
+        <f>($B$18*J6*(1+J6)^$B$9/((1+J6)^$B$9-1)+$B$20)/$B$19</f>
+        <v/>
+      </c>
+      <c r="L6" s="9">
+        <f>K6/$K$5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Indexation OPEX</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>%/an</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <f>IF(E7&lt;=$B$9,$B$20*(1+$B$7)^(E7-1),0)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>IF(E7&lt;=$B$9,$B$19*(1-$B$8)^(E7-1),0)</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>1/(1+$B$17)^E7</f>
+        <v/>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K7" s="8">
+        <f>($B$18*J7*(1+J7)^$B$9/((1+J7)^$B$9-1)+$B$20)/$B$19</f>
+        <v/>
+      </c>
+      <c r="L7" s="9">
+        <f>K7/$K$5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dégradation</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>%/an</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <f>IF(E8&lt;=$B$9,$B$20*(1+$B$7)^(E8-1),0)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IF(E8&lt;=$B$9,$B$19*(1-$B$8)^(E8-1),0)</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>1/(1+$B$17)^E8</f>
+        <v/>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K8" s="8">
+        <f>($B$18*J8*(1+J8)^$B$9/((1+J8)^$B$9-1)+$B$20)/$B$19</f>
+        <v/>
+      </c>
+      <c r="L8" s="9">
+        <f>K8/$K$5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Durée de vie</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>années (max 40)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <f>IF(E9&lt;=$B$9,$B$20*(1+$B$7)^(E9-1),0)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>IF(E9&lt;=$B$9,$B$19*(1-$B$8)^(E9-1),0)</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>1/(1+$B$17)^E9</f>
+        <v/>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K9" s="8">
+        <f>($B$18*J9*(1+J9)^$B$9/((1+J9)^$B$9-1)+$B$20)/$B$19</f>
+        <v/>
+      </c>
+      <c r="L9" s="9">
+        <f>K9/$K$5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Part de la dette</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10">
+        <f>IF(E10&lt;=$B$9,$B$20*(1+$B$7)^(E10-1),0)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>IF(E10&lt;=$B$9,$B$19*(1-$B$8)^(E10-1),0)</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>1/(1+$B$17)^E10</f>
+        <v/>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K10" s="8">
+        <f>($B$18*J10*(1+J10)^$B$9/((1+J10)^$B$9-1)+$B$20)/$B$19</f>
+        <v/>
+      </c>
+      <c r="L10" s="9">
+        <f>K10/$K$5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Coût de la dette</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <f>IF(E11&lt;=$B$9,$B$20*(1+$B$7)^(E11-1),0)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>IF(E11&lt;=$B$9,$B$19*(1-$B$8)^(E11-1),0)</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>1/(1+$B$17)^E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Coût des fonds propres</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12">
+        <f>IF(E12&lt;=$B$9,$B$20*(1+$B$7)^(E12-1),0)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>IF(E12&lt;=$B$9,$B$19*(1-$B$8)^(E12-1),0)</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>1/(1+$B$17)^E12</f>
+        <v/>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Valeurs par défaut = cas illustratif de la proposition (50 MWp, 50 M USD, 90 GWh, 0,75 M USD/an, 25 ans). Résultats illustratifs, pas des coûts observés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Taux d'impôt</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <f>IF(E13&lt;=$B$9,$B$20*(1+$B$7)^(E13-1),0)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>IF(E13&lt;=$B$9,$B$19*(1-$B$8)^(E13-1),0)</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>1/(1+$B$17)^E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WACC calculé</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
+        <f>B10*B11*(1-B13)+(1-B10)*B12</f>
+        <v/>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>11</v>
+      </c>
+      <c r="F14">
+        <f>IF(E14&lt;=$B$9,$B$20*(1+$B$7)^(E14-1),0)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>IF(E14&lt;=$B$9,$B$19*(1-$B$8)^(E14-1),0)</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>1/(1+$B$17)^E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WACC retenu (vide = calculé)</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <f>IF(E15&lt;=$B$9,$B$20*(1+$B$7)^(E15-1),0)</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>IF(E15&lt;=$B$9,$B$19*(1-$B$8)^(E15-1),0)</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>1/(1+$B$17)^E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" t="n">
+        <v>13</v>
+      </c>
+      <c r="F16">
+        <f>IF(E16&lt;=$B$9,$B$20*(1+$B$7)^(E16-1),0)</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>IF(E16&lt;=$B$9,$B$19*(1-$B$8)^(E16-1),0)</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>1/(1+$B$17)^E16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Taux d'actualisation</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>IF(ISBLANK(B15),B14,B15)</f>
+        <v/>
+      </c>
+      <c r="E17" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17">
+        <f>IF(E17&lt;=$B$9,$B$20*(1+$B$7)^(E17-1),0)</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>IF(E17&lt;=$B$9,$B$19*(1-$B$8)^(E17-1),0)</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>1/(1+$B$17)^E17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CAPEX total (USD)</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>B3*1000*B4</f>
+        <v/>
+      </c>
+      <c r="E18" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18">
+        <f>IF(E18&lt;=$B$9,$B$20*(1+$B$7)^(E18-1),0)</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>IF(E18&lt;=$B$9,$B$19*(1-$B$8)^(E18-1),0)</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>1/(1+$B$17)^E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Production année 1 (MWh)</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>B3*B5</f>
+        <v/>
+      </c>
+      <c r="E19" t="n">
+        <v>16</v>
+      </c>
+      <c r="F19">
+        <f>IF(E19&lt;=$B$9,$B$20*(1+$B$7)^(E19-1),0)</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>IF(E19&lt;=$B$9,$B$19*(1-$B$8)^(E19-1),0)</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>1/(1+$B$17)^E19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>OPEX année 1 (USD)</t>
+        </is>
+      </c>
+      <c r="B20">
+        <f>B3*1000*B6</f>
+        <v/>
+      </c>
+      <c r="E20" t="n">
+        <v>17</v>
+      </c>
+      <c r="F20">
+        <f>IF(E20&lt;=$B$9,$B$20*(1+$B$7)^(E20-1),0)</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>IF(E20&lt;=$B$9,$B$19*(1-$B$8)^(E20-1),0)</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>1/(1+$B$17)^E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Coûts actualisés (USD)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <f>B18+SUMPRODUCT(F4:F43,H4:H43)</f>
+        <v/>
+      </c>
+      <c r="E21" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21">
+        <f>IF(E21&lt;=$B$9,$B$20*(1+$B$7)^(E21-1),0)</f>
+        <v/>
+      </c>
+      <c r="G21">
+        <f>IF(E21&lt;=$B$9,$B$19*(1-$B$8)^(E21-1),0)</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>1/(1+$B$17)^E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Production actualisée (MWh)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>SUMPRODUCT(G4:G43,H4:H43)</f>
+        <v/>
+      </c>
+      <c r="E22" t="n">
+        <v>19</v>
+      </c>
+      <c r="F22">
+        <f>IF(E22&lt;=$B$9,$B$20*(1+$B$7)^(E22-1),0)</f>
+        <v/>
+      </c>
+      <c r="G22">
+        <f>IF(E22&lt;=$B$9,$B$19*(1-$B$8)^(E22-1),0)</f>
+        <v/>
+      </c>
+      <c r="H22">
+        <f>1/(1+$B$17)^E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>LCOE (USD/MWh)</t>
+        </is>
+      </c>
+      <c r="B23" s="11">
+        <f>B21/B22</f>
+        <v/>
+      </c>
+      <c r="E23" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23">
+        <f>IF(E23&lt;=$B$9,$B$20*(1+$B$7)^(E23-1),0)</f>
+        <v/>
+      </c>
+      <c r="G23">
+        <f>IF(E23&lt;=$B$9,$B$19*(1-$B$8)^(E23-1),0)</f>
+        <v/>
+      </c>
+      <c r="H23">
+        <f>1/(1+$B$17)^E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Facteur de charge DC</t>
+        </is>
+      </c>
+      <c r="B24" s="9">
+        <f>B5/8760</f>
+        <v/>
+      </c>
+      <c r="E24" t="n">
+        <v>21</v>
+      </c>
+      <c r="F24">
+        <f>IF(E24&lt;=$B$9,$B$20*(1+$B$7)^(E24-1),0)</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>IF(E24&lt;=$B$9,$B$19*(1-$B$8)^(E24-1),0)</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>1/(1+$B$17)^E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="E25" t="n">
+        <v>22</v>
+      </c>
+      <c r="F25">
+        <f>IF(E25&lt;=$B$9,$B$20*(1+$B$7)^(E25-1),0)</f>
+        <v/>
+      </c>
+      <c r="G25">
+        <f>IF(E25&lt;=$B$9,$B$19*(1-$B$8)^(E25-1),0)</f>
+        <v/>
+      </c>
+      <c r="H25">
+        <f>1/(1+$B$17)^E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" t="n">
+        <v>23</v>
+      </c>
+      <c r="F26">
+        <f>IF(E26&lt;=$B$9,$B$20*(1+$B$7)^(E26-1),0)</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>IF(E26&lt;=$B$9,$B$19*(1-$B$8)^(E26-1),0)</f>
+        <v/>
+      </c>
+      <c r="H26">
+        <f>1/(1+$B$17)^E26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27">
+        <f>IF(E27&lt;=$B$9,$B$20*(1+$B$7)^(E27-1),0)</f>
+        <v/>
+      </c>
+      <c r="G27">
+        <f>IF(E27&lt;=$B$9,$B$19*(1-$B$8)^(E27-1),0)</f>
+        <v/>
+      </c>
+      <c r="H27">
+        <f>1/(1+$B$17)^E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" t="n">
+        <v>25</v>
+      </c>
+      <c r="F28">
+        <f>IF(E28&lt;=$B$9,$B$20*(1+$B$7)^(E28-1),0)</f>
+        <v/>
+      </c>
+      <c r="G28">
+        <f>IF(E28&lt;=$B$9,$B$19*(1-$B$8)^(E28-1),0)</f>
+        <v/>
+      </c>
+      <c r="H28">
+        <f>1/(1+$B$17)^E28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="E29" t="n">
+        <v>26</v>
+      </c>
+      <c r="F29">
+        <f>IF(E29&lt;=$B$9,$B$20*(1+$B$7)^(E29-1),0)</f>
+        <v/>
+      </c>
+      <c r="G29">
+        <f>IF(E29&lt;=$B$9,$B$19*(1-$B$8)^(E29-1),0)</f>
+        <v/>
+      </c>
+      <c r="H29">
+        <f>1/(1+$B$17)^E29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="E30" t="n">
+        <v>27</v>
+      </c>
+      <c r="F30">
+        <f>IF(E30&lt;=$B$9,$B$20*(1+$B$7)^(E30-1),0)</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>IF(E30&lt;=$B$9,$B$19*(1-$B$8)^(E30-1),0)</f>
+        <v/>
+      </c>
+      <c r="H30">
+        <f>1/(1+$B$17)^E30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" t="n">
+        <v>28</v>
+      </c>
+      <c r="F31">
+        <f>IF(E31&lt;=$B$9,$B$20*(1+$B$7)^(E31-1),0)</f>
+        <v/>
+      </c>
+      <c r="G31">
+        <f>IF(E31&lt;=$B$9,$B$19*(1-$B$8)^(E31-1),0)</f>
+        <v/>
+      </c>
+      <c r="H31">
+        <f>1/(1+$B$17)^E31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="E32" t="n">
+        <v>29</v>
+      </c>
+      <c r="F32">
+        <f>IF(E32&lt;=$B$9,$B$20*(1+$B$7)^(E32-1),0)</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>IF(E32&lt;=$B$9,$B$19*(1-$B$8)^(E32-1),0)</f>
+        <v/>
+      </c>
+      <c r="H32">
+        <f>1/(1+$B$17)^E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="E33" t="n">
+        <v>30</v>
+      </c>
+      <c r="F33">
+        <f>IF(E33&lt;=$B$9,$B$20*(1+$B$7)^(E33-1),0)</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>IF(E33&lt;=$B$9,$B$19*(1-$B$8)^(E33-1),0)</f>
+        <v/>
+      </c>
+      <c r="H33">
+        <f>1/(1+$B$17)^E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="E34" t="n">
+        <v>31</v>
+      </c>
+      <c r="F34">
+        <f>IF(E34&lt;=$B$9,$B$20*(1+$B$7)^(E34-1),0)</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>IF(E34&lt;=$B$9,$B$19*(1-$B$8)^(E34-1),0)</f>
+        <v/>
+      </c>
+      <c r="H34">
+        <f>1/(1+$B$17)^E34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" t="n">
+        <v>32</v>
+      </c>
+      <c r="F35">
+        <f>IF(E35&lt;=$B$9,$B$20*(1+$B$7)^(E35-1),0)</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>IF(E35&lt;=$B$9,$B$19*(1-$B$8)^(E35-1),0)</f>
+        <v/>
+      </c>
+      <c r="H35">
+        <f>1/(1+$B$17)^E35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" t="n">
+        <v>33</v>
+      </c>
+      <c r="F36">
+        <f>IF(E36&lt;=$B$9,$B$20*(1+$B$7)^(E36-1),0)</f>
+        <v/>
+      </c>
+      <c r="G36">
+        <f>IF(E36&lt;=$B$9,$B$19*(1-$B$8)^(E36-1),0)</f>
+        <v/>
+      </c>
+      <c r="H36">
+        <f>1/(1+$B$17)^E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" t="n">
+        <v>34</v>
+      </c>
+      <c r="F37">
+        <f>IF(E37&lt;=$B$9,$B$20*(1+$B$7)^(E37-1),0)</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>IF(E37&lt;=$B$9,$B$19*(1-$B$8)^(E37-1),0)</f>
+        <v/>
+      </c>
+      <c r="H37">
+        <f>1/(1+$B$17)^E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="E38" t="n">
+        <v>35</v>
+      </c>
+      <c r="F38">
+        <f>IF(E38&lt;=$B$9,$B$20*(1+$B$7)^(E38-1),0)</f>
+        <v/>
+      </c>
+      <c r="G38">
+        <f>IF(E38&lt;=$B$9,$B$19*(1-$B$8)^(E38-1),0)</f>
+        <v/>
+      </c>
+      <c r="H38">
+        <f>1/(1+$B$17)^E38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="E39" t="n">
+        <v>36</v>
+      </c>
+      <c r="F39">
+        <f>IF(E39&lt;=$B$9,$B$20*(1+$B$7)^(E39-1),0)</f>
+        <v/>
+      </c>
+      <c r="G39">
+        <f>IF(E39&lt;=$B$9,$B$19*(1-$B$8)^(E39-1),0)</f>
+        <v/>
+      </c>
+      <c r="H39">
+        <f>1/(1+$B$17)^E39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="E40" t="n">
+        <v>37</v>
+      </c>
+      <c r="F40">
+        <f>IF(E40&lt;=$B$9,$B$20*(1+$B$7)^(E40-1),0)</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>IF(E40&lt;=$B$9,$B$19*(1-$B$8)^(E40-1),0)</f>
+        <v/>
+      </c>
+      <c r="H40">
+        <f>1/(1+$B$17)^E40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="E41" t="n">
+        <v>38</v>
+      </c>
+      <c r="F41">
+        <f>IF(E41&lt;=$B$9,$B$20*(1+$B$7)^(E41-1),0)</f>
+        <v/>
+      </c>
+      <c r="G41">
+        <f>IF(E41&lt;=$B$9,$B$19*(1-$B$8)^(E41-1),0)</f>
+        <v/>
+      </c>
+      <c r="H41">
+        <f>1/(1+$B$17)^E41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="E42" t="n">
+        <v>39</v>
+      </c>
+      <c r="F42">
+        <f>IF(E42&lt;=$B$9,$B$20*(1+$B$7)^(E42-1),0)</f>
+        <v/>
+      </c>
+      <c r="G42">
+        <f>IF(E42&lt;=$B$9,$B$19*(1-$B$8)^(E42-1),0)</f>
+        <v/>
+      </c>
+      <c r="H42">
+        <f>1/(1+$B$17)^E42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="E43" t="n">
+        <v>40</v>
+      </c>
+      <c r="F43">
+        <f>IF(E43&lt;=$B$9,$B$20*(1+$B$7)^(E43-1),0)</f>
+        <v/>
+      </c>
+      <c r="G43">
+        <f>IF(E43&lt;=$B$9,$B$19*(1-$B$8)^(E43-1),0)</f>
+        <v/>
+      </c>
+      <c r="H43">
+        <f>1/(1+$B$17)^E43</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Volet B — solaire captif contre diesel/HFO, du point de vue de l'industriel. Valeurs par défaut illustratives, à remplacer par celles du site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Puissance PV</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>énergie utile (MWh)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>OPEX (USD)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>année</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>flux net (USD)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>économie carburant (USD)</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>actualisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAPEX spécifique (PV + stockage éventuel)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>900</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>USD/kWp</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f>-B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Production spécifique année 1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1700</v>
+      </c>
+      <c r="C5">
+        <f>IF(E5&lt;=$B$13,$B$17*(1-$B$12)^(E5-1),0)</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>IF(E5&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <f>G5-D5</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>C5*$B$18*(1+$B$11)^(E5-1)</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>1/(1+$B$14)^E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Part de la production solaire consommée</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C6">
+        <f>IF(E6&lt;=$B$13,$B$17*(1-$B$12)^(E6-1),0)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>IF(E6&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <f>G6-D6</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>C6*$B$18*(1+$B$11)^(E6-1)</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>1/(1+$B$14)^E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>OPEX solaire</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <f>IF(E7&lt;=$B$13,$B$17*(1-$B$12)^(E7-1),0)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>IF(E7&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <f>G7-D7</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>C7*$B$18*(1+$B$11)^(E7-1)</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>1/(1+$B$14)^E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Prix du carburant livré sur site</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C8">
+        <f>IF(E8&lt;=$B$13,$B$17*(1-$B$12)^(E8-1),0)</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IF(E8&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <f>G8-D8</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>C8*$B$18*(1+$B$11)^(E8-1)</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>1/(1+$B$14)^E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Consommation spécifique du groupe</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C9">
+        <f>IF(E9&lt;=$B$13,$B$17*(1-$B$12)^(E9-1),0)</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>IF(E9&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <f>G9-D9</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>C9*$B$18*(1+$B$11)^(E9-1)</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>1/(1+$B$14)^E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>O&amp;M variable du groupe</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <f>IF(E10&lt;=$B$13,$B$17*(1-$B$12)^(E10-1),0)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>IF(E10&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <f>G10-D10</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>C10*$B$18*(1+$B$11)^(E10-1)</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>1/(1+$B$14)^E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Indexation du prix du carburant</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C11">
+        <f>IF(E11&lt;=$B$13,$B$17*(1-$B$12)^(E11-1),0)</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>IF(E11&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11">
+        <f>G11-D11</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>C11*$B$18*(1+$B$11)^(E11-1)</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>1/(1+$B$14)^E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dégradation PV</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C12">
+        <f>IF(E12&lt;=$B$13,$B$17*(1-$B$12)^(E12-1),0)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>IF(E12&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12">
+        <f>G12-D12</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>C12*$B$18*(1+$B$11)^(E12-1)</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>1/(1+$B$14)^E12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Durée d'analyse</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <f>IF(E13&lt;=$B$13,$B$17*(1-$B$12)^(E13-1),0)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>IF(E13&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <f>G13-D13</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>C13*$B$18*(1+$B$11)^(E13-1)</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>1/(1+$B$14)^E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Taux d'actualisation de l'industriel</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C14">
+        <f>IF(E14&lt;=$B$13,$B$17*(1-$B$12)^(E14-1),0)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>IF(E14&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <f>G14-D14</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>C14*$B$18*(1+$B$11)^(E14-1)</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>1/(1+$B$14)^E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15">
+        <f>IF(E15&lt;=$B$13,$B$17*(1-$B$12)^(E15-1),0)</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>IF(E15&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15">
+        <f>G15-D15</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>C15*$B$18*(1+$B$11)^(E15-1)</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>1/(1+$B$14)^E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CAPEX total (USD)</t>
+        </is>
+      </c>
+      <c r="B16" s="12">
+        <f>B3*1000*B4</f>
+        <v/>
+      </c>
+      <c r="C16">
+        <f>IF(E16&lt;=$B$13,$B$17*(1-$B$12)^(E16-1),0)</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>IF(E16&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <f>G16-D16</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>C16*$B$18*(1+$B$11)^(E16-1)</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>1/(1+$B$14)^E16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Énergie solaire utile année 1 (MWh)</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>B3*B5*B6</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>IF(E17&lt;=$B$13,$B$17*(1-$B$12)^(E17-1),0)</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>IF(E17&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E17" t="n">
+        <v>13</v>
+      </c>
+      <c r="F17">
+        <f>G17-D17</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>C17*$B$18*(1+$B$11)^(E17-1)</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>1/(1+$B$14)^E17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Coût diesel évité (USD/MWh)</t>
+        </is>
+      </c>
+      <c r="B18" s="8">
+        <f>B8*B9*1000+B10</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>IF(E18&lt;=$B$13,$B$17*(1-$B$12)^(E18-1),0)</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>IF(E18&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E18" t="n">
+        <v>14</v>
+      </c>
+      <c r="F18">
+        <f>G18-D18</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>C18*$B$18*(1+$B$11)^(E18-1)</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>1/(1+$B$14)^E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>OPEX solaire (USD/an)</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>B3*1000*B7</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>IF(E19&lt;=$B$13,$B$17*(1-$B$12)^(E19-1),0)</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>IF(E19&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F19">
+        <f>G19-D19</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>C19*$B$18*(1+$B$11)^(E19-1)</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>1/(1+$B$14)^E19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Économie nette année 1 (USD)</t>
+        </is>
+      </c>
+      <c r="B20" s="12">
+        <f>B17*B18-B19</f>
+        <v/>
+      </c>
+      <c r="C20">
+        <f>IF(E20&lt;=$B$13,$B$17*(1-$B$12)^(E20-1),0)</f>
+        <v/>
+      </c>
+      <c r="D20">
+        <f>IF(E20&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20">
+        <f>G20-D20</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>C20*$B$18*(1+$B$11)^(E20-1)</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>1/(1+$B$14)^E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Temps de retour simple (années)</t>
+        </is>
+      </c>
+      <c r="B21" s="8">
+        <f>IF(B20&lt;=0,"jamais",B16/B20)</f>
+        <v/>
+      </c>
+      <c r="C21">
+        <f>IF(E21&lt;=$B$13,$B$17*(1-$B$12)^(E21-1),0)</f>
+        <v/>
+      </c>
+      <c r="D21">
+        <f>IF(E21&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E21" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21">
+        <f>G21-D21</f>
+        <v/>
+      </c>
+      <c r="G21">
+        <f>C21*$B$18*(1+$B$11)^(E21-1)</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>1/(1+$B$14)^E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>VAN (USD)</t>
+        </is>
+      </c>
+      <c r="B22" s="12">
+        <f>NPV(B14,F5:F34)+F4</f>
+        <v/>
+      </c>
+      <c r="C22">
+        <f>IF(E22&lt;=$B$13,$B$17*(1-$B$12)^(E22-1),0)</f>
+        <v/>
+      </c>
+      <c r="D22">
+        <f>IF(E22&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E22" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22">
+        <f>G22-D22</f>
+        <v/>
+      </c>
+      <c r="G22">
+        <f>C22*$B$18*(1+$B$11)^(E22-1)</f>
+        <v/>
+      </c>
+      <c r="H22">
+        <f>1/(1+$B$14)^E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="B23" s="9">
+        <f>IFERROR(IRR(F4:F34),"n.d.")</f>
+        <v/>
+      </c>
+      <c r="C23">
+        <f>IF(E23&lt;=$B$13,$B$17*(1-$B$12)^(E23-1),0)</f>
+        <v/>
+      </c>
+      <c r="D23">
+        <f>IF(E23&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E23" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23">
+        <f>G23-D23</f>
+        <v/>
+      </c>
+      <c r="G23">
+        <f>C23*$B$18*(1+$B$11)^(E23-1)</f>
+        <v/>
+      </c>
+      <c r="H23">
+        <f>1/(1+$B$14)^E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LCOE solaire (USD/MWh utile)</t>
+        </is>
+      </c>
+      <c r="B24" s="8">
+        <f>(B16+SUMPRODUCT(D5:D34,H5:H34))/SUMPRODUCT(C5:C34,H5:H34)</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>IF(E24&lt;=$B$13,$B$17*(1-$B$12)^(E24-1),0)</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>IF(E24&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E24" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24">
+        <f>G24-D24</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>C24*$B$18*(1+$B$11)^(E24-1)</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>1/(1+$B$14)^E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25">
+        <f>IF(E25&lt;=$B$13,$B$17*(1-$B$12)^(E25-1),0)</f>
+        <v/>
+      </c>
+      <c r="D25">
+        <f>IF(E25&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E25" t="n">
+        <v>21</v>
+      </c>
+      <c r="F25">
+        <f>G25-D25</f>
+        <v/>
+      </c>
+      <c r="G25">
+        <f>C25*$B$18*(1+$B$11)^(E25-1)</f>
+        <v/>
+      </c>
+      <c r="H25">
+        <f>1/(1+$B$14)^E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Limites : pas de coût de stockage spécifique, pas de valeur de la continuité de service ni d'investissement évité dans les groupes ; à ajouter projet par projet. Le TRI élevé obtenu par défaut n'est pas calibré : la presse évoque 3 à 7 ans de retour pour Fekola (PV + stockage), contre moins de 2 ans ici.</t>
+        </is>
+      </c>
+      <c r="C26">
+        <f>IF(E26&lt;=$B$13,$B$17*(1-$B$12)^(E26-1),0)</f>
+        <v/>
+      </c>
+      <c r="D26">
+        <f>IF(E26&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E26" t="n">
+        <v>22</v>
+      </c>
+      <c r="F26">
+        <f>G26-D26</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>C26*$B$18*(1+$B$11)^(E26-1)</f>
+        <v/>
+      </c>
+      <c r="H26">
+        <f>1/(1+$B$14)^E26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27">
+        <f>IF(E27&lt;=$B$13,$B$17*(1-$B$12)^(E27-1),0)</f>
+        <v/>
+      </c>
+      <c r="D27">
+        <f>IF(E27&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E27" t="n">
+        <v>23</v>
+      </c>
+      <c r="F27">
+        <f>G27-D27</f>
+        <v/>
+      </c>
+      <c r="G27">
+        <f>C27*$B$18*(1+$B$11)^(E27-1)</f>
+        <v/>
+      </c>
+      <c r="H27">
+        <f>1/(1+$B$14)^E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28">
+        <f>IF(E28&lt;=$B$13,$B$17*(1-$B$12)^(E28-1),0)</f>
+        <v/>
+      </c>
+      <c r="D28">
+        <f>IF(E28&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28">
+        <f>G28-D28</f>
+        <v/>
+      </c>
+      <c r="G28">
+        <f>C28*$B$18*(1+$B$11)^(E28-1)</f>
+        <v/>
+      </c>
+      <c r="H28">
+        <f>1/(1+$B$14)^E28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29">
+        <f>IF(E29&lt;=$B$13,$B$17*(1-$B$12)^(E29-1),0)</f>
+        <v/>
+      </c>
+      <c r="D29">
+        <f>IF(E29&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E29" t="n">
+        <v>25</v>
+      </c>
+      <c r="F29">
+        <f>G29-D29</f>
+        <v/>
+      </c>
+      <c r="G29">
+        <f>C29*$B$18*(1+$B$11)^(E29-1)</f>
+        <v/>
+      </c>
+      <c r="H29">
+        <f>1/(1+$B$14)^E29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30">
+        <f>IF(E30&lt;=$B$13,$B$17*(1-$B$12)^(E30-1),0)</f>
+        <v/>
+      </c>
+      <c r="D30">
+        <f>IF(E30&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E30" t="n">
+        <v>26</v>
+      </c>
+      <c r="F30">
+        <f>G30-D30</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>C30*$B$18*(1+$B$11)^(E30-1)</f>
+        <v/>
+      </c>
+      <c r="H30">
+        <f>1/(1+$B$14)^E30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31">
+        <f>IF(E31&lt;=$B$13,$B$17*(1-$B$12)^(E31-1),0)</f>
+        <v/>
+      </c>
+      <c r="D31">
+        <f>IF(E31&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E31" t="n">
+        <v>27</v>
+      </c>
+      <c r="F31">
+        <f>G31-D31</f>
+        <v/>
+      </c>
+      <c r="G31">
+        <f>C31*$B$18*(1+$B$11)^(E31-1)</f>
+        <v/>
+      </c>
+      <c r="H31">
+        <f>1/(1+$B$14)^E31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32">
+        <f>IF(E32&lt;=$B$13,$B$17*(1-$B$12)^(E32-1),0)</f>
+        <v/>
+      </c>
+      <c r="D32">
+        <f>IF(E32&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E32" t="n">
+        <v>28</v>
+      </c>
+      <c r="F32">
+        <f>G32-D32</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>C32*$B$18*(1+$B$11)^(E32-1)</f>
+        <v/>
+      </c>
+      <c r="H32">
+        <f>1/(1+$B$14)^E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33">
+        <f>IF(E33&lt;=$B$13,$B$17*(1-$B$12)^(E33-1),0)</f>
+        <v/>
+      </c>
+      <c r="D33">
+        <f>IF(E33&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E33" t="n">
+        <v>29</v>
+      </c>
+      <c r="F33">
+        <f>G33-D33</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>C33*$B$18*(1+$B$11)^(E33-1)</f>
+        <v/>
+      </c>
+      <c r="H33">
+        <f>1/(1+$B$14)^E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34">
+        <f>IF(E34&lt;=$B$13,$B$17*(1-$B$12)^(E34-1),0)</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>IF(E34&lt;=$B$13,$B$19,0)</f>
+        <v/>
+      </c>
+      <c r="E34" t="n">
+        <v>30</v>
+      </c>
+      <c r="F34">
+        <f>G34-D34</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>C34*$B$18*(1+$B$11)^(E34-1)</f>
+        <v/>
+      </c>
+      <c r="H34">
+        <f>1/(1+$B$14)^E34</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Volet C — coût complet du service d'un mini-réseau (production, distribution, gestion commerciale) et subvention nécessaire. Valeurs par défaut illustratives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Puissance PV</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>kWp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAPEX production (PV, batteries, groupe)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>USD/kWp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Production utile année 1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>kWh/kWp/an</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Nombre de clients</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>branchements</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAPEX distribution par client</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>USD/client</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OPEX technique (y c. annuité de remplacement des batteries)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>USD/kWp/an</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Coût de gestion commerciale par client</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>USD/client/an</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pertes et impayés</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>% de la production</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Taux d'actualisation</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Durée d'analyse</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>années</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tarif autorisé</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>USD/kWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CRF</t>
+        </is>
+      </c>
+      <c r="B15" s="13">
+        <f>B11*(1+B11)^B12/((1+B11)^B12-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Énergie vendue (MWh/an)</t>
+        </is>
+      </c>
+      <c r="B16" s="8">
+        <f>B3*B5*(1-B10)/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Consommation par client (kWh/mois)</t>
+        </is>
+      </c>
+      <c r="B17" s="8">
+        <f>B16*1000/B6/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Coût de production (USD/MWh vendu)</t>
+        </is>
+      </c>
+      <c r="B18" s="8">
+        <f>(B3*B4*B15+B3*B8)/B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Coût de distribution (USD/MWh vendu)</t>
+        </is>
+      </c>
+      <c r="B19" s="8">
+        <f>B6*B7*B15/B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Coût commercial (USD/MWh vendu)</t>
+        </is>
+      </c>
+      <c r="B20" s="8">
+        <f>B6*B9/B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Coût complet du service (USD/MWh)</t>
+        </is>
+      </c>
+      <c r="B21" s="11">
+        <f>B18+B19+B20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Subvention d'investissement nécessaire (USD)</t>
+        </is>
+      </c>
+      <c r="B22" s="12">
+        <f>MAX(0,B21-B13*1000)*B16/B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Subvention par branchement (USD)</t>
+        </is>
+      </c>
+      <c r="B23" s="12">
+        <f>B22/B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>La consommation par client (B17) pèse sur le coût de distribution et le coût commercial : c'est le principal levier de la question économique du volet C.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3166,7 +6030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3407,6 +6271,157 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B-MLI-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MLI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fekola (mine d'or)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>B2Gold</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>en service</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PV + BESS + HFO</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>S08;S09</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>C - presse spécialisée</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>CAPEX = budget approuvé, pas le coût final ; stockage 13,5 vs 15,4 MWh ; année de mise en service à confirmer</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Mines</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Autoproduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B-MRT-001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MRT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Tasiast (mine d'or)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kinross</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>en service</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I3" t="n">
+        <v>34</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PV + BESS (18 MW) + thermique</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>S10;S11</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>C - presse spécialisée</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Couverture ~20 % = prévision ; CAPEX annoncé, pas le coût final</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Mines</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Autoproduction</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="F2:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -3426,7 +6441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO1"/>
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3679,6 +6694,64 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C-COD-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Goma Ndosho (métro-réseau)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Nuru</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>en service</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PV + BESS + groupes de secours (~364 kW)</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>C - presse spécialisée</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Coût, tarif et nombre de clients non publiés dans les sources consultées</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>Privé</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="F2:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -3698,7 +6771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4076,6 +7149,356 @@
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B-MLI-001</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>puissance_mwp</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>déclarée</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DC/AC non précisé ; extension à 52 MW annoncée (phase II)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B-MLI-001</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>stockage_mwh</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MWh</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>déclarée</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>13,5 MWh dans l'annonce de 2019 (S08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B-MLI-001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>capex_total</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>déclarée</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Budget approuvé en 2019, pas le coût final</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B-MLI-001</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fioul_evite</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>13100000</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>l/an</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>déclarée</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Prévision ; ~13 Ml rapportés pour 2024 par la presse</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B-MRT-001</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>puissance_mwp</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>déclarée</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DC/AC non précisé</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B-MRT-001</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>batterie_mw</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>déclarée</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Puissance de la batterie, pas son énergie (MWh inconnus)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B-MRT-001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>capex_total</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>déclarée</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Annonce de 2022, pas le coût final</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B-MRT-001</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>annee_mise_en_service</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>année</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>déclarée</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Premier courant solaire déc. 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C-COD-001</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>puissance_mwp</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>déclarée</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DC/AC non précisé</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C-COD-001</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>annee_mise_en_service</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>année</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>déclarée</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Inauguration le 4 février 2020</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4093,7 +7516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4387,6 +7810,248 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mining Weekly</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B2Gold approves $38m hybrid energy project for Mali mine</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.miningweekly.com/article/b2gold-approves-3m-hybrid-energy-project-for-mali-mine-2019-10-14</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fekola : budget approuvé 38 M USD ; 13,1 Ml de fioul lourd évités par an (prévision)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Africa Energy Portal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Malian gold mine powered by 30 MW/15.4 MWh solar-plus-storage</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://africa-energy-portal.org/news/malian-gold-mine-powered-30-mw154-mwh-solar-plus-storage</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fekola : 30 MW / 15,4 MWh construits (13,5 MWh annoncés initialement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mining Weekly</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Kinross makes $55m solar investment at Tasiast</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.miningweekly.com/article/kinross-makes-55m-solar-investment-at-tasiast-2022-02-17</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tasiast : 55 M USD, 34 MW PV, batterie 18 MW, ~20 % des besoins du site</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Engineering News</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Tasiast solar project, Mauritania – update</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.engineeringnews.co.za/article/tasiastsolar-project-mauritania-update-2024-02-23</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Premier courant solaire en décembre 2023 ; mise en service batterie/EMS début 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Afrik 21</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DRC: Nuru connects 1.3 MW solar off-grid hybrid in Goma</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://afrik21.africa/en/drc-nuru-connects-1-3-mw-solar-off-grid-hybrid-in-goma</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goma (Ndosho) : 1,3 MW, batteries, ~364 kW de groupes de secours, inauguré le 4 février 2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BloombergNEF / SEforALL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>State of the Global Mini-grids Market Report 2020</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://about.bnef.com/insights/clean-energy/solar-mini-grids-set-to-play-critical-role-in-achieving-universal-electricity-access-with-right-policy-support/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>LCOE des mini-réseaux solaires hybrides isolés : 0,49 à 0,68 USD/kWh (6 pays étudiés)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ESMAP / Banque mondiale</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mini Grids for Half a Billion People (2019)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www1.villanova.edu/content/dam/villanova/engineering/energy-workshop/ESMAP%20Mini%20Grids%20-%20Executive%20Summary.pdf</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Objectif : 0,20 USD/kWh pour les mini-réseaux solaires hybrides d'ici 2030 (projection)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4398,1056 +8063,251 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Modèle LCOE — cellules jaunes modifiables. Investissement en année 0, flux en années 1..n.</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>volet</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>indicateur</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>valeur</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>unité</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>année</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LCOE moyen pondéré PV, monde</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>43</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>USD/MWh</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>observée (agrégat)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>S01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Puissance</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MWp</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>année</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>OPEX (USD)</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>production (MWh)</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>facteur d'actualisation</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Sensibilité au WACC (sans dégradation ni indexation : (CAPEX x CRF + OPEX) / E)</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Coût d'installation moyen PV, Afrique</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1093</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>USD/kW</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>déclarée (secondaire)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>S02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAPEX spécifique</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>USD/kWp</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WACC supposé par IRENA, Afrique</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <f>IF(E4&lt;=$B$9,$B$20*(1+$B$7)^(E4-1),0)</f>
-        <v/>
-      </c>
-      <c r="G4">
-        <f>IF(E4&lt;=$B$9,$B$19*(1-$B$8)^(E4-1),0)</f>
-        <v/>
-      </c>
-      <c r="H4">
-        <f>1/(1+$B$17)^E4</f>
-        <v/>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>LCOE (USD/MWh)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>écart vs 4 %</t>
+        <v>2024</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hypothèse IRENA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>S01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Production spécifique année 1</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>kWh/kWp/an</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LCOE mini-réseaux solaires hybrides isolés (min)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>490</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>USD/MWh</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <f>IF(E5&lt;=$B$9,$B$20*(1+$B$7)^(E5-1),0)</f>
-        <v/>
-      </c>
-      <c r="G5">
-        <f>IF(E5&lt;=$B$9,$B$19*(1-$B$8)^(E5-1),0)</f>
-        <v/>
-      </c>
-      <c r="H5">
-        <f>1/(1+$B$17)^E5</f>
-        <v/>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K5" s="6">
-        <f>($B$18*J5*(1+J5)^$B$9/((1+J5)^$B$9-1)+$B$20)/$B$19</f>
-        <v/>
-      </c>
-      <c r="L5" s="7">
-        <f>K5/$K$5-1</f>
-        <v/>
+        <v>2020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>observée (étude)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OPEX année 1</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>USD/kWp/an</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LCOE mini-réseaux solaires hybrides isolés (max)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>680</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>USD/MWh</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <f>IF(E6&lt;=$B$9,$B$20*(1+$B$7)^(E6-1),0)</f>
-        <v/>
-      </c>
-      <c r="G6">
-        <f>IF(E6&lt;=$B$9,$B$19*(1-$B$8)^(E6-1),0)</f>
-        <v/>
-      </c>
-      <c r="H6">
-        <f>1/(1+$B$17)^E6</f>
-        <v/>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K6" s="6">
-        <f>($B$18*J6*(1+J6)^$B$9/((1+J6)^$B$9-1)+$B$20)/$B$19</f>
-        <v/>
-      </c>
-      <c r="L6" s="7">
-        <f>K6/$K$5-1</f>
-        <v/>
+        <v>2020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>observée (étude)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Indexation OPEX</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>%/an</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Objectif LCOE mini-réseaux 2030</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>USD/MWh</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <f>IF(E7&lt;=$B$9,$B$20*(1+$B$7)^(E7-1),0)</f>
-        <v/>
-      </c>
-      <c r="G7">
-        <f>IF(E7&lt;=$B$9,$B$19*(1-$B$8)^(E7-1),0)</f>
-        <v/>
-      </c>
-      <c r="H7">
-        <f>1/(1+$B$17)^E7</f>
-        <v/>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K7" s="6">
-        <f>($B$18*J7*(1+J7)^$B$9/((1+J7)^$B$9-1)+$B$20)/$B$19</f>
-        <v/>
-      </c>
-      <c r="L7" s="7">
-        <f>K7/$K$5-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Dégradation</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>%/an</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8">
-        <f>IF(E8&lt;=$B$9,$B$20*(1+$B$7)^(E8-1),0)</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>IF(E8&lt;=$B$9,$B$19*(1-$B$8)^(E8-1),0)</f>
-        <v/>
-      </c>
-      <c r="H8">
-        <f>1/(1+$B$17)^E8</f>
-        <v/>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K8" s="6">
-        <f>($B$18*J8*(1+J8)^$B$9/((1+J8)^$B$9-1)+$B$20)/$B$19</f>
-        <v/>
-      </c>
-      <c r="L8" s="7">
-        <f>K8/$K$5-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Durée de vie</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>années (max 40)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9">
-        <f>IF(E9&lt;=$B$9,$B$20*(1+$B$7)^(E9-1),0)</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>IF(E9&lt;=$B$9,$B$19*(1-$B$8)^(E9-1),0)</f>
-        <v/>
-      </c>
-      <c r="H9">
-        <f>1/(1+$B$17)^E9</f>
-        <v/>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="K9" s="6">
-        <f>($B$18*J9*(1+J9)^$B$9/((1+J9)^$B$9-1)+$B$20)/$B$19</f>
-        <v/>
-      </c>
-      <c r="L9" s="7">
-        <f>K9/$K$5-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Part de la dette</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10">
-        <f>IF(E10&lt;=$B$9,$B$20*(1+$B$7)^(E10-1),0)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>IF(E10&lt;=$B$9,$B$19*(1-$B$8)^(E10-1),0)</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>1/(1+$B$17)^E10</f>
-        <v/>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K10" s="6">
-        <f>($B$18*J10*(1+J10)^$B$9/((1+J10)^$B$9-1)+$B$20)/$B$19</f>
-        <v/>
-      </c>
-      <c r="L10" s="7">
-        <f>K10/$K$5-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Coût de la dette</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11">
-        <f>IF(E11&lt;=$B$9,$B$20*(1+$B$7)^(E11-1),0)</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>IF(E11&lt;=$B$9,$B$19*(1-$B$8)^(E11-1),0)</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>1/(1+$B$17)^E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Coût des fonds propres</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>9</v>
-      </c>
-      <c r="F12">
-        <f>IF(E12&lt;=$B$9,$B$20*(1+$B$7)^(E12-1),0)</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>IF(E12&lt;=$B$9,$B$19*(1-$B$8)^(E12-1),0)</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>1/(1+$B$17)^E12</f>
-        <v/>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>Valeurs par défaut = cas illustratif de la proposition (50 MWp, 50 M USD, 90 GWh, 0,75 M USD/an, 25 ans). Résultats illustratifs, pas des coûts observés.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Taux d'impôt</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13">
-        <f>IF(E13&lt;=$B$9,$B$20*(1+$B$7)^(E13-1),0)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>IF(E13&lt;=$B$9,$B$19*(1-$B$8)^(E13-1),0)</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>1/(1+$B$17)^E13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WACC calculé</t>
-        </is>
-      </c>
-      <c r="B14" s="7">
-        <f>B10*B11*(1-B13)+(1-B10)*B12</f>
-        <v/>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>11</v>
-      </c>
-      <c r="F14">
-        <f>IF(E14&lt;=$B$9,$B$20*(1+$B$7)^(E14-1),0)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>IF(E14&lt;=$B$9,$B$19*(1-$B$8)^(E14-1),0)</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>1/(1+$B$17)^E14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>WACC retenu (vide = calculé)</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>12</v>
-      </c>
-      <c r="F15">
-        <f>IF(E15&lt;=$B$9,$B$20*(1+$B$7)^(E15-1),0)</f>
-        <v/>
-      </c>
-      <c r="G15">
-        <f>IF(E15&lt;=$B$9,$B$19*(1-$B$8)^(E15-1),0)</f>
-        <v/>
-      </c>
-      <c r="H15">
-        <f>1/(1+$B$17)^E15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="E16" t="n">
-        <v>13</v>
-      </c>
-      <c r="F16">
-        <f>IF(E16&lt;=$B$9,$B$20*(1+$B$7)^(E16-1),0)</f>
-        <v/>
-      </c>
-      <c r="G16">
-        <f>IF(E16&lt;=$B$9,$B$19*(1-$B$8)^(E16-1),0)</f>
-        <v/>
-      </c>
-      <c r="H16">
-        <f>1/(1+$B$17)^E16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Taux d'actualisation</t>
-        </is>
-      </c>
-      <c r="B17" s="7">
-        <f>IF(ISBLANK(B15),B14,B15)</f>
-        <v/>
-      </c>
-      <c r="E17" t="n">
-        <v>14</v>
-      </c>
-      <c r="F17">
-        <f>IF(E17&lt;=$B$9,$B$20*(1+$B$7)^(E17-1),0)</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>IF(E17&lt;=$B$9,$B$19*(1-$B$8)^(E17-1),0)</f>
-        <v/>
-      </c>
-      <c r="H17">
-        <f>1/(1+$B$17)^E17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CAPEX total (USD)</t>
-        </is>
-      </c>
-      <c r="B18">
-        <f>B3*1000*B4</f>
-        <v/>
-      </c>
-      <c r="E18" t="n">
-        <v>15</v>
-      </c>
-      <c r="F18">
-        <f>IF(E18&lt;=$B$9,$B$20*(1+$B$7)^(E18-1),0)</f>
-        <v/>
-      </c>
-      <c r="G18">
-        <f>IF(E18&lt;=$B$9,$B$19*(1-$B$8)^(E18-1),0)</f>
-        <v/>
-      </c>
-      <c r="H18">
-        <f>1/(1+$B$17)^E18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Production année 1 (MWh)</t>
-        </is>
-      </c>
-      <c r="B19">
-        <f>B3*B5</f>
-        <v/>
-      </c>
-      <c r="E19" t="n">
-        <v>16</v>
-      </c>
-      <c r="F19">
-        <f>IF(E19&lt;=$B$9,$B$20*(1+$B$7)^(E19-1),0)</f>
-        <v/>
-      </c>
-      <c r="G19">
-        <f>IF(E19&lt;=$B$9,$B$19*(1-$B$8)^(E19-1),0)</f>
-        <v/>
-      </c>
-      <c r="H19">
-        <f>1/(1+$B$17)^E19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>OPEX année 1 (USD)</t>
-        </is>
-      </c>
-      <c r="B20">
-        <f>B3*1000*B6</f>
-        <v/>
-      </c>
-      <c r="E20" t="n">
-        <v>17</v>
-      </c>
-      <c r="F20">
-        <f>IF(E20&lt;=$B$9,$B$20*(1+$B$7)^(E20-1),0)</f>
-        <v/>
-      </c>
-      <c r="G20">
-        <f>IF(E20&lt;=$B$9,$B$19*(1-$B$8)^(E20-1),0)</f>
-        <v/>
-      </c>
-      <c r="H20">
-        <f>1/(1+$B$17)^E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Coûts actualisés (USD)</t>
-        </is>
-      </c>
-      <c r="B21">
-        <f>B18+SUMPRODUCT(F4:F43,H4:H43)</f>
-        <v/>
-      </c>
-      <c r="E21" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21">
-        <f>IF(E21&lt;=$B$9,$B$20*(1+$B$7)^(E21-1),0)</f>
-        <v/>
-      </c>
-      <c r="G21">
-        <f>IF(E21&lt;=$B$9,$B$19*(1-$B$8)^(E21-1),0)</f>
-        <v/>
-      </c>
-      <c r="H21">
-        <f>1/(1+$B$17)^E21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Production actualisée (MWh)</t>
-        </is>
-      </c>
-      <c r="B22">
-        <f>SUMPRODUCT(G4:G43,H4:H43)</f>
-        <v/>
-      </c>
-      <c r="E22" t="n">
-        <v>19</v>
-      </c>
-      <c r="F22">
-        <f>IF(E22&lt;=$B$9,$B$20*(1+$B$7)^(E22-1),0)</f>
-        <v/>
-      </c>
-      <c r="G22">
-        <f>IF(E22&lt;=$B$9,$B$19*(1-$B$8)^(E22-1),0)</f>
-        <v/>
-      </c>
-      <c r="H22">
-        <f>1/(1+$B$17)^E22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>LCOE (USD/MWh)</t>
-        </is>
-      </c>
-      <c r="B23" s="10">
-        <f>B21/B22</f>
-        <v/>
-      </c>
-      <c r="E23" t="n">
-        <v>20</v>
-      </c>
-      <c r="F23">
-        <f>IF(E23&lt;=$B$9,$B$20*(1+$B$7)^(E23-1),0)</f>
-        <v/>
-      </c>
-      <c r="G23">
-        <f>IF(E23&lt;=$B$9,$B$19*(1-$B$8)^(E23-1),0)</f>
-        <v/>
-      </c>
-      <c r="H23">
-        <f>1/(1+$B$17)^E23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Facteur de charge DC</t>
-        </is>
-      </c>
-      <c r="B24" s="7">
-        <f>B5/8760</f>
-        <v/>
-      </c>
-      <c r="E24" t="n">
-        <v>21</v>
-      </c>
-      <c r="F24">
-        <f>IF(E24&lt;=$B$9,$B$20*(1+$B$7)^(E24-1),0)</f>
-        <v/>
-      </c>
-      <c r="G24">
-        <f>IF(E24&lt;=$B$9,$B$19*(1-$B$8)^(E24-1),0)</f>
-        <v/>
-      </c>
-      <c r="H24">
-        <f>1/(1+$B$17)^E24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="E25" t="n">
-        <v>22</v>
-      </c>
-      <c r="F25">
-        <f>IF(E25&lt;=$B$9,$B$20*(1+$B$7)^(E25-1),0)</f>
-        <v/>
-      </c>
-      <c r="G25">
-        <f>IF(E25&lt;=$B$9,$B$19*(1-$B$8)^(E25-1),0)</f>
-        <v/>
-      </c>
-      <c r="H25">
-        <f>1/(1+$B$17)^E25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="E26" t="n">
-        <v>23</v>
-      </c>
-      <c r="F26">
-        <f>IF(E26&lt;=$B$9,$B$20*(1+$B$7)^(E26-1),0)</f>
-        <v/>
-      </c>
-      <c r="G26">
-        <f>IF(E26&lt;=$B$9,$B$19*(1-$B$8)^(E26-1),0)</f>
-        <v/>
-      </c>
-      <c r="H26">
-        <f>1/(1+$B$17)^E26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="E27" t="n">
-        <v>24</v>
-      </c>
-      <c r="F27">
-        <f>IF(E27&lt;=$B$9,$B$20*(1+$B$7)^(E27-1),0)</f>
-        <v/>
-      </c>
-      <c r="G27">
-        <f>IF(E27&lt;=$B$9,$B$19*(1-$B$8)^(E27-1),0)</f>
-        <v/>
-      </c>
-      <c r="H27">
-        <f>1/(1+$B$17)^E27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="E28" t="n">
-        <v>25</v>
-      </c>
-      <c r="F28">
-        <f>IF(E28&lt;=$B$9,$B$20*(1+$B$7)^(E28-1),0)</f>
-        <v/>
-      </c>
-      <c r="G28">
-        <f>IF(E28&lt;=$B$9,$B$19*(1-$B$8)^(E28-1),0)</f>
-        <v/>
-      </c>
-      <c r="H28">
-        <f>1/(1+$B$17)^E28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="E29" t="n">
-        <v>26</v>
-      </c>
-      <c r="F29">
-        <f>IF(E29&lt;=$B$9,$B$20*(1+$B$7)^(E29-1),0)</f>
-        <v/>
-      </c>
-      <c r="G29">
-        <f>IF(E29&lt;=$B$9,$B$19*(1-$B$8)^(E29-1),0)</f>
-        <v/>
-      </c>
-      <c r="H29">
-        <f>1/(1+$B$17)^E29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="E30" t="n">
-        <v>27</v>
-      </c>
-      <c r="F30">
-        <f>IF(E30&lt;=$B$9,$B$20*(1+$B$7)^(E30-1),0)</f>
-        <v/>
-      </c>
-      <c r="G30">
-        <f>IF(E30&lt;=$B$9,$B$19*(1-$B$8)^(E30-1),0)</f>
-        <v/>
-      </c>
-      <c r="H30">
-        <f>1/(1+$B$17)^E30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="E31" t="n">
-        <v>28</v>
-      </c>
-      <c r="F31">
-        <f>IF(E31&lt;=$B$9,$B$20*(1+$B$7)^(E31-1),0)</f>
-        <v/>
-      </c>
-      <c r="G31">
-        <f>IF(E31&lt;=$B$9,$B$19*(1-$B$8)^(E31-1),0)</f>
-        <v/>
-      </c>
-      <c r="H31">
-        <f>1/(1+$B$17)^E31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="E32" t="n">
-        <v>29</v>
-      </c>
-      <c r="F32">
-        <f>IF(E32&lt;=$B$9,$B$20*(1+$B$7)^(E32-1),0)</f>
-        <v/>
-      </c>
-      <c r="G32">
-        <f>IF(E32&lt;=$B$9,$B$19*(1-$B$8)^(E32-1),0)</f>
-        <v/>
-      </c>
-      <c r="H32">
-        <f>1/(1+$B$17)^E32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="E33" t="n">
-        <v>30</v>
-      </c>
-      <c r="F33">
-        <f>IF(E33&lt;=$B$9,$B$20*(1+$B$7)^(E33-1),0)</f>
-        <v/>
-      </c>
-      <c r="G33">
-        <f>IF(E33&lt;=$B$9,$B$19*(1-$B$8)^(E33-1),0)</f>
-        <v/>
-      </c>
-      <c r="H33">
-        <f>1/(1+$B$17)^E33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="E34" t="n">
-        <v>31</v>
-      </c>
-      <c r="F34">
-        <f>IF(E34&lt;=$B$9,$B$20*(1+$B$7)^(E34-1),0)</f>
-        <v/>
-      </c>
-      <c r="G34">
-        <f>IF(E34&lt;=$B$9,$B$19*(1-$B$8)^(E34-1),0)</f>
-        <v/>
-      </c>
-      <c r="H34">
-        <f>1/(1+$B$17)^E34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="E35" t="n">
-        <v>32</v>
-      </c>
-      <c r="F35">
-        <f>IF(E35&lt;=$B$9,$B$20*(1+$B$7)^(E35-1),0)</f>
-        <v/>
-      </c>
-      <c r="G35">
-        <f>IF(E35&lt;=$B$9,$B$19*(1-$B$8)^(E35-1),0)</f>
-        <v/>
-      </c>
-      <c r="H35">
-        <f>1/(1+$B$17)^E35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="E36" t="n">
-        <v>33</v>
-      </c>
-      <c r="F36">
-        <f>IF(E36&lt;=$B$9,$B$20*(1+$B$7)^(E36-1),0)</f>
-        <v/>
-      </c>
-      <c r="G36">
-        <f>IF(E36&lt;=$B$9,$B$19*(1-$B$8)^(E36-1),0)</f>
-        <v/>
-      </c>
-      <c r="H36">
-        <f>1/(1+$B$17)^E36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="E37" t="n">
-        <v>34</v>
-      </c>
-      <c r="F37">
-        <f>IF(E37&lt;=$B$9,$B$20*(1+$B$7)^(E37-1),0)</f>
-        <v/>
-      </c>
-      <c r="G37">
-        <f>IF(E37&lt;=$B$9,$B$19*(1-$B$8)^(E37-1),0)</f>
-        <v/>
-      </c>
-      <c r="H37">
-        <f>1/(1+$B$17)^E37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="E38" t="n">
-        <v>35</v>
-      </c>
-      <c r="F38">
-        <f>IF(E38&lt;=$B$9,$B$20*(1+$B$7)^(E38-1),0)</f>
-        <v/>
-      </c>
-      <c r="G38">
-        <f>IF(E38&lt;=$B$9,$B$19*(1-$B$8)^(E38-1),0)</f>
-        <v/>
-      </c>
-      <c r="H38">
-        <f>1/(1+$B$17)^E38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="E39" t="n">
-        <v>36</v>
-      </c>
-      <c r="F39">
-        <f>IF(E39&lt;=$B$9,$B$20*(1+$B$7)^(E39-1),0)</f>
-        <v/>
-      </c>
-      <c r="G39">
-        <f>IF(E39&lt;=$B$9,$B$19*(1-$B$8)^(E39-1),0)</f>
-        <v/>
-      </c>
-      <c r="H39">
-        <f>1/(1+$B$17)^E39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="E40" t="n">
-        <v>37</v>
-      </c>
-      <c r="F40">
-        <f>IF(E40&lt;=$B$9,$B$20*(1+$B$7)^(E40-1),0)</f>
-        <v/>
-      </c>
-      <c r="G40">
-        <f>IF(E40&lt;=$B$9,$B$19*(1-$B$8)^(E40-1),0)</f>
-        <v/>
-      </c>
-      <c r="H40">
-        <f>1/(1+$B$17)^E40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="E41" t="n">
-        <v>38</v>
-      </c>
-      <c r="F41">
-        <f>IF(E41&lt;=$B$9,$B$20*(1+$B$7)^(E41-1),0)</f>
-        <v/>
-      </c>
-      <c r="G41">
-        <f>IF(E41&lt;=$B$9,$B$19*(1-$B$8)^(E41-1),0)</f>
-        <v/>
-      </c>
-      <c r="H41">
-        <f>1/(1+$B$17)^E41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="E42" t="n">
-        <v>39</v>
-      </c>
-      <c r="F42">
-        <f>IF(E42&lt;=$B$9,$B$20*(1+$B$7)^(E42-1),0)</f>
-        <v/>
-      </c>
-      <c r="G42">
-        <f>IF(E42&lt;=$B$9,$B$19*(1-$B$8)^(E42-1),0)</f>
-        <v/>
-      </c>
-      <c r="H42">
-        <f>1/(1+$B$17)^E42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="E43" t="n">
-        <v>40</v>
-      </c>
-      <c r="F43">
-        <f>IF(E43&lt;=$B$9,$B$20*(1+$B$7)^(E43-1),0)</f>
-        <v/>
-      </c>
-      <c r="G43">
-        <f>IF(E43&lt;=$B$9,$B$19*(1-$B$8)^(E43-1),0)</f>
-        <v/>
-      </c>
-      <c r="H43">
-        <f>1/(1+$B$17)^E43</f>
-        <v/>
+        <v>2030</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/studies/solaire-afrique/etude_solaire_afrique.xlsx
+++ b/studies/solaire-afrique/etude_solaire_afrique.xlsx
@@ -3433,7 +3433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -3516,17 +3516,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>corroboré (secondaire)</t>
+          <t>confirmé</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cité par pv magazine d'après IRENA ; non retrouvé dans le résumé IRENA</t>
+          <t>Rapport complet IRENA 2024, Table 3.1 p. 95</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S15</t>
         </is>
       </c>
     </row>
@@ -3538,15 +3538,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>non vérifié</t>
+          <t>confirmé</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Absent du résumé IRENA ; à contrôler dans le rapport complet ou la base IRENA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Rapport complet IRENA 2024, Table 3.3 p. 106</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3556,42 +3560,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>non vérifié</t>
+          <t>confirmé</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Une source secondaire citant l'édition suivante d'IRENA donne 3 520 USD/kW et 222 USD/MWh pour 2015 : les séries historiques sont révisées d'une édition à l'autre</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Rapport complet IRENA 2024 (USD 2024). L'édition 2025 donne 3 520 USD/kW et 222 USD/MWh pour 2015 en USD 2025 : ne pas mélanger les éditions</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>S15;S16</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tableau WACC 4–14 % (43,9 à 89,3 USD/MWh)</t>
+          <t>(nouveau) Afrique 2025 : 837 USD/kW et 52 USD/MWh</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>confirmé (calcul)</t>
+          <t>confirmé</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reproduit : 43,9 / 51,8 / 60,4 / 69,5 / 79,2 / 89,2 ; écarts d'arrondi ≤ 0,1</t>
+          <t>Rapport complet IRENA 2025, Tables 3.1 et 3.2 ; -76 % et -77 % depuis 2015</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>lcoe.py</t>
+          <t>S16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>+80 % de LCOE entre WACC 4 % et 12 %</t>
+          <t>Tableau WACC 4–14 % (43,9 à 89,3 USD/MWh)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3601,7 +3609,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+80,4 %</t>
+          <t>Reproduit : 43,9 / 51,8 / 60,4 / 69,5 / 79,2 / 89,2 ; écarts d'arrondi ≤ 0,1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3613,42 +3621,64 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ngonye / Bangweulu</t>
+          <t>+80 % de LCOE entre WACC 4 % et 12 %</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>précisé</t>
+          <t>confirmé (calcul)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bangweulu = 6,015 USc/kWh (Neoen/First Solar) ; Ngonye = 7,84 USc/kWh (Enel)</t>
+          <t>+80,4 %</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>S04;S05</t>
+          <t>lcoe.py</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Ngonye / Bangweulu</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>précisé</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bangweulu = 6,015 USc/kWh (Neoen/First Solar) ; Ngonye = 7,84 USc/kWh (Enel)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>S04;S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Kael et Kahone</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>confirmé</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>3,98 et 3,80 c EUR/kWh, mise en service mai 2021</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>S06;S07</t>
         </is>
@@ -7516,7 +7546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8052,6 +8082,76 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>IRENA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Renewable Power Generation Costs in 2024 (rapport complet)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2025/Jul/IRENA_TEC_RPGC_in_2024_2025.pdf</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Afrique PV : LCOE 0,074 (2024) / 0,225 (2015) USD2024/kWh, Table 3.3 p. 106 ; coût d'installation 1 093 (2024) / 3 437 (2015) USD2024/kW, Table 3.1 p. 95 ; WACC PV 12 %, fig. 1.13 p. 41</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IRENA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Renewable Power Generation Costs in 2025 (rapport complet)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2026/Jul/IRENA_TEC_RPGC_in_2025_2026.pdf</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Afrique PV : coût d'installation 837 (2025) / 3 520 (2015) USD2025/kW, Table 3.1 p. 62 ; LCOE 52 (2025) / 222 (2015) USD2025/MWh, Table 3.2 p. 71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8063,7 +8163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8153,15 +8253,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Coût d'installation moyen PV, Afrique</t>
+          <t>IRENA RPGC 2024 — LCOE moyen pondéré PV, Afrique (USD 2024)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1093</v>
+        <v>74</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>USD/kW</t>
+          <t>USD/MWh</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -8169,12 +8269,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>déclarée (secondaire)</t>
+          <t>observée (agrégat)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S15</t>
         </is>
       </c>
     </row>
@@ -8186,44 +8286,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WACC supposé par IRENA, Afrique</t>
+          <t>IRENA RPGC 2024 — LCOE moyen pondéré PV, Afrique (USD 2024)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.12</v>
+        <v>225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>USD/MWh</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>hypothèse IRENA</t>
+          <t>observée (agrégat)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LCOE mini-réseaux solaires hybrides isolés (min)</t>
+          <t>IRENA RPGC 2024 — LCOE PV Afrique, 5e percentile</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>490</v>
+        <v>49</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -8231,32 +8331,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>observée (étude)</t>
+          <t>observée (agrégat)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LCOE mini-réseaux solaires hybrides isolés (max)</t>
+          <t>IRENA RPGC 2024 — LCOE PV Afrique, 95e percentile</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>680</v>
+        <v>186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -8264,47 +8364,344 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>observée (étude)</t>
+          <t>observée (agrégat)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IRENA RPGC 2024 — coût d'installation PV, Afrique (USD 2024)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1093</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>USD/kW</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>observée (agrégat)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IRENA RPGC 2024 — coût d'installation PV, Afrique (USD 2024)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3437</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>USD/kW</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>observée (agrégat)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IRENA RPGC 2024 — WACC réel supposé, PV Afrique</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hypothèse IRENA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IRENA RPGC 2025 — LCOE moyen pondéré PV, Afrique (USD 2025)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>52</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>USD/MWh</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>observée (agrégat)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IRENA RPGC 2025 — LCOE moyen pondéré PV, Afrique (USD 2025)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>222</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>USD/MWh</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>observée (agrégat)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IRENA RPGC 2025 — coût d'installation PV, Afrique (USD 2025)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>837</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>USD/kW</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>observée (agrégat)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IRENA RPGC 2025 — coût d'installation PV, Afrique (USD 2025)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3520</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>USD/kW</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>observée (agrégat)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LCOE mini-réseaux solaires hybrides isolés (min)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>490</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>USD/MWh</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>observée (étude)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LCOE mini-réseaux solaires hybrides isolés (max)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>680</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>USD/MWh</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>observée (étude)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Objectif LCOE mini-réseaux 2030</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C16" t="n">
         <v>200</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>USD/MWh</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E16" t="n">
         <v>2030</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>projection</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>S14</t>
         </is>
